--- a/logs/experiments_not_systematic/sorted_by_experiment/3_reps_change_agressive_vs_tipical.xlsx
+++ b/logs/experiments_not_systematic/sorted_by_experiment/3_reps_change_agressive_vs_tipical.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/sorted_by_experiment/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_not_systematic/sorted_by_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45D18929-58A1-42BA-8977-D4794573B8A1}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D2F04E46CFB4ACB3E20D455D6CCDA693EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02705F5D-8421-45AA-9759-6ED188CC8D20}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-5460" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main_results" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="81" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2934,7 +2934,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2344CA01-057D-40A1-A333-ECFC3F3316D5}" name="TablaDinámica1" cacheId="81" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2344CA01-057D-40A1-A333-ECFC3F3316D5}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:H10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="95">
     <pivotField numFmtId="164" showAll="0"/>
@@ -9410,14 +9410,14 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
